--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ff8dd6ff8aa4a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c43640f794e4f32"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c43640f794e4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5dfc1086ed14301"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5dfc1086ed14301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R44ff8f91b99c4b91"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R44ff8f91b99c4b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7bc658e4e0c04ba1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7bc658e4e0c04ba1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R654d39992fc645df"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R654d39992fc645df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R947627e807144d4b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R947627e807144d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8109effcfa1f4030"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8109effcfa1f4030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87f8b17e6e13477b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R87f8b17e6e13477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb4a334e446b447b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb4a334e446b447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4474341de304739"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4474341de304739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4bce749e04dc40c0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4bce749e04dc40c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R54a64056dd5146bd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R54a64056dd5146bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc2b57ff89d554d86"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/StyledHeaderRow/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc2b57ff89d554d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63f41f44389c47dc"/>
   </x:sheets>
 </x:workbook>
 </file>
